--- a/files/九龙-尖沙咀-本木.xlsx
+++ b/files/九龙-尖沙咀-本木.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -845,7 +845,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -987,7 +987,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-10</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-06</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-03</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-03</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-14</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-13</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-12</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-10</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-13</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-14</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-28</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-18</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-13</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-27</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-09</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-10</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-27</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-20</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-14</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-29</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-26</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8812,7 +8812,7 @@
           <t>A1 | 350呎 (1房)
 $1175万
 $33,574/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -8820,7 +8820,7 @@
           <t>A2 | 752呎 (3房)
 $2438万
 $32,420/呎
-(已售)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -8828,7 +8828,7 @@
           <t>A3 | 511呎 (2房)
 $1600万
 $31,311/呎
-(已售)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -8836,7 +8836,7 @@
           <t>A5 | 350呎 (1房)
 $1118万
 $31,943/呎
-(已售)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr"/>
@@ -8853,7 +8853,7 @@
           <t>B2 | 718呎 (3房)
 $2300万
 $32,033/呎
-(已售)</t>
+(23年-09月)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -8861,7 +8861,7 @@
           <t>B3 | 378呎 (1房)
 $1208万
 $31,958/呎
-(已售)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -8885,7 +8885,7 @@
           <t>A1 | 350呎 (1房)
 $1051万
 $30,025/呎
-(已售)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -8901,7 +8901,7 @@
           <t>A3 | 511呎 (2房)
 $1443万
 $28,235/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -8909,7 +8909,7 @@
           <t>A5 | 350呎 (1房)
 $1025万
 $29,284/呎
-(已售)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
           <t>B1 | 236呎 (开放式)
 $741万
 $31,391/呎
-(已售)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -8926,7 +8926,7 @@
           <t>B2 | 718呎 (3房)
 $1900万
 $26,462/呎
-(已售)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -8934,7 +8934,7 @@
           <t>B3 | 378呎 (1房)
 $1052万
 $27,827/呎
-(已售)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
@@ -8958,7 +8958,7 @@
           <t>A1 | 350呎 (1房)
 $1057万
 $30,195/呎
-(已售)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -8966,7 +8966,7 @@
           <t>A2 | 752呎 (3房)
 $2140万
 $28,456/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -8974,7 +8974,7 @@
           <t>A3 | 511呎 (2房)
 $1322万
 $25,864/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -8982,7 +8982,7 @@
           <t>A5 | 350呎 (1房)
 $998万
 $28,523/呎
-(已售)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr"/>
@@ -8991,7 +8991,7 @@
           <t>B1 | 236呎 (开放式)
 $718万
 $30,409/呎
-(已售)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -8999,7 +8999,7 @@
           <t>B2 | 718呎 (3房)
 $1841万
 $25,636/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -9007,7 +9007,7 @@
           <t>B3 | 378呎 (1房)
 $1034万
 $27,351/呎
-(已售)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -9015,7 +9015,7 @@
           <t>B5 | 335呎 (1房)
 $910万
 $27,152/呎
-(已售)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr"/>
@@ -9031,7 +9031,7 @@
           <t>A1 | 350呎 (1房)
 $1039万
 $29,674/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -9039,7 +9039,7 @@
           <t>A2 | 752呎 (3房)
 $2225万
 $29,593/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9055,7 +9055,7 @@
           <t>A5 | 350呎 (1房)
 $970万
 $27,728/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr"/>
@@ -9064,7 +9064,7 @@
           <t>B1 | 233呎 (开放式)
 $711万
 $30,499/呎
-(已售)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -9072,7 +9072,7 @@
           <t>B2 | 721呎 (3房)
 $1961万
 $27,204/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -9080,7 +9080,7 @@
           <t>B3 | 378呎 (1房)
 $1024万
 $27,086/呎
-(已售)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -9088,7 +9088,7 @@
           <t>B5 | 335呎 (1房)
 $900万
 $26,869/呎
-(已售)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr"/>
@@ -9104,7 +9104,7 @@
           <t>A1 | 350呎 (1房)
 $961万
 $27,457/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -9112,7 +9112,7 @@
           <t>A2 | 752呎 (3房)
 $2226万
 $29,605/呎
-(已售)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -9120,7 +9120,7 @@
           <t>A3 | 511呎 (2房)
 $1296万
 $25,370/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -9128,7 +9128,7 @@
           <t>A5 | 350呎 (1房)
 $971万
 $27,734/呎
-(已售)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
@@ -9137,7 +9137,7 @@
           <t>B1 | 236呎 (开放式)
 $697万
 $29,536/呎
-(已售)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -9145,7 +9145,7 @@
           <t>B2 | 718呎 (3房)
 $2040万
 $28,407/呎
-(已售)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -9153,7 +9153,7 @@
           <t>B3 | 378呎 (1房)
 $1014万
 $26,832/呎
-(已售)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -9161,7 +9161,7 @@
           <t>B5 | 335呎 (1房)
 $919万
 $27,442/呎
-(已售)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr"/>
@@ -9177,7 +9177,7 @@
           <t>A1 | 350呎 (1房)
 $962万
 $27,488/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -9185,7 +9185,7 @@
           <t>A2 | 752呎 (3房)
 $2099万
 $27,919/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9193,7 +9193,7 @@
           <t>A3 | 511呎 (2房)
 $1271万
 $24,878/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -9201,7 +9201,7 @@
           <t>A5 | 350呎 (1房)
 $907万
 $25,915/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -9210,7 +9210,7 @@
           <t>B1 | 236呎 (开放式)
 $670万
 $28,395/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -9218,7 +9218,7 @@
           <t>B2 | 718呎 (3房)
 $1943万
 $27,058/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -9226,7 +9226,7 @@
           <t>B3 | 378呎 (1房)
 $995万
 $26,311/呎
-(已售)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -9234,7 +9234,7 @@
           <t>B5 | 335呎 (1房)
 $902万
 $26,913/呎
-(已售)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr"/>
@@ -9250,7 +9250,7 @@
           <t>A1 | 350呎 (1房)
 $913万
 $26,085/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -9266,7 +9266,7 @@
           <t>A3 | 511呎 (2房)
 $1254万
 $24,537/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -9274,7 +9274,7 @@
           <t>A5 | 350呎 (1房)
 $916万
 $26,167/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -9283,7 +9283,7 @@
           <t>B1 | 236呎 (开放式)
 $674万
 $28,542/呎
-(已售)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -9291,7 +9291,7 @@
           <t>B2 | 718呎 (3房)
 $1913万
 $26,640/呎
-(已售)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -9299,7 +9299,7 @@
           <t>B3 | 378呎 (1房)
 $968万
 $25,608/呎
-(已售)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -9307,7 +9307,7 @@
           <t>B5 | 335呎 (1房)
 $846万
 $25,241/呎
-(已售)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr"/>
@@ -9323,7 +9323,7 @@
           <t>A1 | 350呎 (1房)
 $932万
 $26,620/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -9331,7 +9331,7 @@
           <t>A2 | 752呎 (3房)
 $2061万
 $27,411/呎
-(已售)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9339,7 +9339,7 @@
           <t>A3 | 511呎 (2房)
 $1261万
 $24,676/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -9347,7 +9347,7 @@
           <t>A5 | 350呎 (1房)
 $898万
 $25,644/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -9356,7 +9356,7 @@
           <t>B1 | 236呎 (开放式)
 $651万
 $27,594/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -9364,7 +9364,7 @@
           <t>B2 | 718呎 (3房)
 $1906万
 $26,546/呎
-(已售)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -9372,7 +9372,7 @@
           <t>B3 | 378呎 (1房)
 $942万
 $24,918/呎
-(已售)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -9380,7 +9380,7 @@
           <t>B5 | 335呎 (1房)
 $869万
 $25,931/呎
-(已售)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr"/>
@@ -9396,7 +9396,7 @@
           <t>A1 | 350呎 (1房)
 $895万
 $25,559/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -9404,7 +9404,7 @@
           <t>A2 | 752呎 (3房)
 $1949万
 $25,923/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -9412,7 +9412,7 @@
           <t>A3 | 511呎 (2房)
 $1204万
 $23,562/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -9420,7 +9420,7 @@
           <t>A5 | 350呎 (1房)
 $846万
 $24,176/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -9429,7 +9429,7 @@
           <t>B1 | 236呎 (开放式)
 $647万
 $27,405/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -9437,7 +9437,7 @@
           <t>B2 | 721呎 (3房)
 $1804万
 $25,019/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -9445,7 +9445,7 @@
           <t>B3 | 378呎 (1房)
 $932万
 $24,653/呎
-(已售)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -9453,7 +9453,7 @@
           <t>B5 | 335呎 (1房)
 $854万
 $25,495/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr"/>
@@ -9469,7 +9469,7 @@
           <t>A1 | 350呎 (1房)
 $919万
 $26,255/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -9477,7 +9477,7 @@
           <t>A2 | 511呎 (2房)
 $1318万
 $25,796/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9493,7 +9493,7 @@
           <t>A5 | 511呎 (2房)
 $1267万
 $24,802/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -9501,7 +9501,7 @@
           <t>A6 | 350呎 (1房)
 $841万
 $24,023/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -9509,7 +9509,7 @@
           <t>B1 | 335呎 (1房)
 $851万
 $25,403/呎
-(已售)</t>
+(21年-02月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -9517,7 +9517,7 @@
           <t>B2 | 378呎 (1房)
 $892万
 $23,598/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -9525,7 +9525,7 @@
           <t>B3 | 256呎 (开放式)
 $643万
 $25,133/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -9533,7 +9533,7 @@
           <t>B5 | 378呎 (1房)
 $891万
 $23,561/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -9541,7 +9541,7 @@
           <t>B6 | 335呎 (1房)
 $801万
 $23,902/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9556,7 @@
           <t>A1 | 350呎 (1房)
 $895万
 $25,582/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -9564,7 +9564,7 @@
           <t>A2 | 511呎 (2房)
 $1247万
 $24,403/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -9572,7 +9572,7 @@
           <t>A3 | 256呎 (开放式)
 $701万
 $27,372/呎
-(已售)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -9580,7 +9580,7 @@
           <t>A5 | 511呎 (2房)
 $1187万
 $23,233/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -9588,7 +9588,7 @@
           <t>A6 | 350呎 (1房)
 $860万
 $24,572/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -9596,7 +9596,7 @@
           <t>B1 | 335呎 (1房)
 $845万
 $25,229/呎
-(已售)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -9604,7 +9604,7 @@
           <t>B2 | 378呎 (1房)
 $930万
 $24,603/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -9612,7 +9612,7 @@
           <t>B3 | 256呎 (开放式)
 $639万
 $24,959/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -9620,7 +9620,7 @@
           <t>B5 | 378呎 (1房)
 $902万
 $23,854/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -9628,7 +9628,7 @@
           <t>B6 | 335呎 (1房)
 $819万
 $24,446/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
     </row>
@@ -9643,7 +9643,7 @@
           <t>A1 | 350呎 (1房)
 $868万
 $24,791/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -9651,7 +9651,7 @@
           <t>A2 | 511呎 (2房)
 $1258万
 $24,620/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9659,7 +9659,7 @@
           <t>A3 | 256呎 (开放式)
 $684万
 $26,715/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -9667,7 +9667,7 @@
           <t>A5 | 511呎 (2房)
 $1186万
 $23,219/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -9675,7 +9675,7 @@
           <t>A6 | 350呎 (1房)
 $829万
 $23,692/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -9683,7 +9683,7 @@
           <t>B1 | 335呎 (1房)
 $839万
 $25,054/呎
-(已售)</t>
+(21年-02月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -9691,7 +9691,7 @@
           <t>B2 | 378呎 (1房)
 $888万
 $23,503/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -9699,7 +9699,7 @@
           <t>B3 | 256呎 (开放式)
 $610万
 $23,826/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -9707,7 +9707,7 @@
           <t>B5 | 378呎 (1房)
 $878万
 $23,226/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -9715,7 +9715,7 @@
           <t>B6 | 335呎 (1房)
 $790万
 $23,568/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9730,7 @@
           <t>A1 | 350呎 (1房)
 $887万
 $25,347/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -9738,7 +9738,7 @@
           <t>A2 | 511呎 (2房)
 $1237万
 $24,215/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -9746,7 +9746,7 @@
           <t>A3 | 256呎 (开放式)
 $688万
 $26,892/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -9754,7 +9754,7 @@
           <t>A5 | 511呎 (2房)
 $1213万
 $23,735/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -9762,7 +9762,7 @@
           <t>A6 | 350呎 (1房)
 $832万
 $23,766/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -9770,7 +9770,7 @@
           <t>B1 | 335呎 (1房)
 $825万
 $24,641/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -9778,7 +9778,7 @@
           <t>B2 | 378呎 (1房)
 $908万
 $24,027/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -9786,7 +9786,7 @@
           <t>B3 | 256呎 (开放式)
 $606万
 $23,656/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -9794,7 +9794,7 @@
           <t>B5 | 378呎 (1房)
 $889万
 $23,511/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -9817,7 +9817,7 @@
           <t>A1 | 350呎 (1房)
 $847万
 $24,201/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -9825,7 +9825,7 @@
           <t>A2 | 511呎 (2房)
 $1216万
 $23,801/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9833,7 +9833,7 @@
           <t>A3 | 256呎 (开放式)
 $668万
 $26,076/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -9841,7 +9841,7 @@
           <t>A5 | 511呎 (2房)
 $1158万
 $22,658/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -9849,7 +9849,7 @@
           <t>A6 | 350呎 (1房)
 $818万
 $23,361/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -9857,7 +9857,7 @@
           <t>B1 | 335呎 (1房)
 $820万
 $24,466/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -9865,7 +9865,7 @@
           <t>B2 | 378呎 (1房)
 $867万
 $22,940/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -9873,7 +9873,7 @@
           <t>B3 | 256呎 (开放式)
 $625万
 $24,421/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -9881,7 +9881,7 @@
           <t>B5 | 378呎 (1房)
 $865万
 $22,893/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -9889,7 +9889,7 @@
           <t>B6 | 335呎 (1房)
 $786万
 $23,469/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
     </row>
@@ -9904,7 +9904,7 @@
           <t>A1 | 350呎 (1房)
 $866万
 $24,750/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -9912,7 +9912,7 @@
           <t>A2 | 511呎 (2房)
 $1231万
 $24,095/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -9920,7 +9920,7 @@
           <t>A3 | 256呎 (开放式)
 $675万
 $26,386/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -9928,7 +9928,7 @@
           <t>A5 | 511呎 (2房)
 $1161万
 $22,722/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -9936,7 +9936,7 @@
           <t>A6 | 350呎 (1房)
 $812万
 $23,194/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -9944,7 +9944,7 @@
           <t>B1 | 335呎 (1房)
 $814万
 $24,295/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -9952,7 +9952,7 @@
           <t>B2 | 378呎 (1房)
 $895万
 $23,687/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -9960,7 +9960,7 @@
           <t>B3 | 256呎 (开放式)
 $603万
 $23,547/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -9968,7 +9968,7 @@
           <t>B5 | 378呎 (1房)
 $876万
 $23,171/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -9976,7 +9976,7 @@
           <t>B6 | 335呎 (1房)
 $773万
 $23,068/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
     </row>
@@ -9991,7 +9991,7 @@
           <t>A1 | 350呎 (1房)
 $835万
 $23,859/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -9999,7 +9999,7 @@
           <t>A2 | 511呎 (2房)
 $1211万
 $23,697/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -10007,7 +10007,7 @@
           <t>A3 | 256呎 (开放式)
 $658万
 $25,701/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -10015,7 +10015,7 @@
           <t>A5 | 511呎 (2房)
 $1137万
 $22,247/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -10023,7 +10023,7 @@
           <t>A6 | 350呎 (1房)
 $800万
 $22,863/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -10031,7 +10031,7 @@
           <t>B1 | 335呎 (1房)
 $797万
 $23,801/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -10039,7 +10039,7 @@
           <t>B2 | 378呎 (1房)
 $849万
 $22,448/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -10047,7 +10047,7 @@
           <t>B3 | 256呎 (开放式)
 $594万
 $23,199/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -10055,7 +10055,7 @@
           <t>B5 | 378呎 (1房)
 $846万
 $22,390/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -10063,7 +10063,7 @@
           <t>B6 | 335呎 (1房)
 $772万
 $23,048/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
           <t>A1 | 350呎 (1房)
 $829万
 $23,686/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -10086,7 +10086,7 @@
           <t>A2 | 511呎 (2房)
 $1190万
 $23,287/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -10094,7 +10094,7 @@
           <t>A3 | 256呎 (开放式)
 $666万
 $26,007/呎
-(已售)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -10102,7 +10102,7 @@
           <t>A5 | 511呎 (2房)
 $1124万
 $22,001/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -10110,7 +10110,7 @@
           <t>A6 | 350呎 (1房)
 $792万
 $22,614/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -10118,7 +10118,7 @@
           <t>B1 | 335呎 (1房)
 $781万
 $23,314/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -10126,7 +10126,7 @@
           <t>B2 | 378呎 (1房)
 $873万
 $23,092/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -10134,7 +10134,7 @@
           <t>B3 | 256呎 (开放式)
 $581万
 $22,708/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -10142,7 +10142,7 @@
           <t>B5 | 378呎 (1房)
 $845万
 $22,362/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -10150,7 +10150,7 @@
           <t>B6 | 335呎 (1房)
 $756万
 $22,566/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
           <t>A1 | 350呎 (1房)
 $831万
 $23,754/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -10173,7 +10173,7 @@
           <t>A2 | 511呎 (2房)
 $1193万
 $23,350/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -10181,7 +10181,7 @@
           <t>A3 | 256呎 (开放式)
 $648万
 $25,326/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -10189,7 +10189,7 @@
           <t>A5 | 511呎 (2房)
 $1112万
 $21,755/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -10197,7 +10197,7 @@
           <t>A6 | 350呎 (1房)
 $783万
 $22,368/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -10205,7 +10205,7 @@
           <t>B1 | 335呎 (1房)
 $757万
 $22,607/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -10213,7 +10213,7 @@
           <t>B2 | 378呎 (1房)
 $838万
 $22,177/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -10221,7 +10221,7 @@
           <t>B3 | 256呎 (开放式)
 $575万
 $22,453/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -10229,7 +10229,7 @@
           <t>B5 | 378呎 (1房)
 $827万
 $21,887/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -10237,7 +10237,7 @@
           <t>B6 | 335呎 (1房)
 $748万
 $22,315/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
           <t>A1 | 328呎 (1房)
 $909万
 $27,710/呎
-(已售)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -10260,7 +10260,7 @@
           <t>A2 | 490呎 (2房)
 $1324万
 $27,013/呎
-(已售)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -10268,7 +10268,7 @@
           <t>A3 | 235呎 (开放式)
 $670万
 $28,504/呎
-(已售)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -10276,7 +10276,7 @@
           <t>A5 | 490呎 (2房)
 $1470万
 $30,000/呎
-(已售)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -10284,7 +10284,7 @@
           <t>A6 | 328呎 (1房)
 $853万
 $26,003/呎
-(已售)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -10292,7 +10292,7 @@
           <t>B1 | 314呎 (1房)
 $871万
 $27,733/呎
-(已售)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -10300,7 +10300,7 @@
           <t>B2 | 356呎 (1房)
 $1160万
 $32,584/呎
-(已售)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -10324,7 +10324,7 @@
           <t>B6 | 313呎 (1房)
 $831万
 $26,543/呎
-(已售)</t>
+(21年-11月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-尖沙咀-本木.xlsx
+++ b/files/九龙-尖沙咀-本木.xlsx
@@ -211,61 +211,61 @@
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -654,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-尖沙咀-本木.xlsx
+++ b/files/九龙-尖沙咀-本木.xlsx
@@ -211,61 +211,61 @@
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -654,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-尖沙咀-本木.xlsx
+++ b/files/九龙-尖沙咀-本木.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,6 +131,11 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -208,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -277,6 +282,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1120,7 +1128,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1129,10 +1137,10 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>9635000</v>
+        <v>9431000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>28761</v>
+        <v>28152</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -2224,19 +2232,19 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>9193140</v>
+        <v>9359000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>27442</v>
+        <v>27937</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -8725,17 +8733,17 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>165</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -8937,12 +8945,12 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J6" s="24" t="inlineStr">
         <is>
           <t>B5 | 335呎 (1房)
-$964万
-$28,761/呎
-(暂停销售)</t>
+$943万
+$28,152/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr"/>
@@ -9156,12 +9164,12 @@
 (21年-05月)</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
+      <c r="J9" s="24" t="inlineStr">
         <is>
           <t>B5 | 335呎 (1房)
-$919万
-$27,442/呎
-(22年-05月)</t>
+$936万
+$27,937/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr"/>

--- a/files/九龙-尖沙咀-本木.xlsx
+++ b/files/九龙-尖沙咀-本木.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,11 +131,6 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -213,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -282,9 +277,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1128,19 +1120,19 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>9431000</v>
+        <v>8110000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>28152</v>
+        <v>24209</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -2232,7 +2224,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -8728,17 +8720,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>166</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8945,12 +8937,12 @@
 (21年-11月)</t>
         </is>
       </c>
-      <c r="J6" s="24" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>B5 | 335呎 (1房)
-$943万
-$28,152/呎
-(已定价未售)</t>
+$811万
+$24,209/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr"/>
@@ -9164,12 +9156,12 @@
 (21年-05月)</t>
         </is>
       </c>
-      <c r="J9" s="24" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>B5 | 335呎 (1房)
 $936万
 $27,937/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr"/>
